--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.8284,0.0439,0.0496,0.0508</t>
-  </si>
-  <si>
-    <t>0.0085,0.0011,0.0011,0.9961</t>
-  </si>
-  <si>
-    <t>0.7373,0.0664,0.0481,0.1561</t>
-  </si>
-  <si>
-    <t>0.1178,0.0044,0.0027,0.9598</t>
-  </si>
-  <si>
-    <t>0.9943,0.0047,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9909,0.0046,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9919,0.0019,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9951,0.0011,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9909,0.0060,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9896,0.0044,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9955,0.0009,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0007,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.8527,0.0276,0.0669,0.0370</t>
-  </si>
-  <si>
-    <t>0.5105,0.0065,0.6350,0.0136</t>
-  </si>
-  <si>
-    <t>0.1466,0.0242,0.8811,0.0064</t>
-  </si>
-  <si>
-    <t>0.1005,0.0084,0.9257,0.0066</t>
-  </si>
-  <si>
-    <t>0.5861,0.0972,0.3835,0.0358</t>
-  </si>
-  <si>
-    <t>0.0439,0.9503,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.2232,0.8575,0.0038,0.0016</t>
-  </si>
-  <si>
-    <t>0.7651,0.3388,0.0111,0.0022</t>
-  </si>
-  <si>
-    <t>0.2578,0.8254,0.0081,0.0016</t>
-  </si>
-  <si>
-    <t>0.0493,0.9495,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.4758,0.0271,0.6519,0.0150</t>
-  </si>
-  <si>
-    <t>0.1812,0.0282,0.8359,0.0174</t>
-  </si>
-  <si>
-    <t>0.1493,0.0362,0.7542,0.0930</t>
-  </si>
-  <si>
-    <t>0.2283,0.0509,0.6831,0.0076</t>
-  </si>
-  <si>
-    <t>0.0840,0.0049,0.9172,0.0346</t>
-  </si>
-  <si>
-    <t>0.0304,0.0029,0.9747,0.0008</t>
-  </si>
-  <si>
-    <t>0.0041,0.0025,0.9819,0.0225</t>
-  </si>
-  <si>
-    <t>0.6396,0.3670,0.0424,0.0019</t>
-  </si>
-  <si>
-    <t>0.5548,0.1505,0.3938,0.0046</t>
-  </si>
-  <si>
-    <t>0.0007,0.0075,0.9959,0.0013</t>
-  </si>
-  <si>
-    <t>0.0119,0.8789,0.4170,0.0009</t>
-  </si>
-  <si>
-    <t>0.5205,0.4179,0.0033,0.0345</t>
-  </si>
-  <si>
-    <t>0.7238,0.2020,0.0898,0.0020</t>
-  </si>
-  <si>
-    <t>0.7263,0.3676,0.0134,0.0020</t>
-  </si>
-  <si>
-    <t>0.1976,0.7467,0.1562,0.0155</t>
-  </si>
-  <si>
-    <t>0.0098,0.9030,0.0658,0.0541</t>
-  </si>
-  <si>
-    <t>0.0083,0.0089,0.9188,0.1197</t>
-  </si>
-  <si>
-    <t>0.0682,0.4416,0.5684,0.0064</t>
-  </si>
-  <si>
-    <t>0.0096,0.0021,0.9690,0.0603</t>
-  </si>
-  <si>
-    <t>0.0534,0.0958,0.8558,0.0071</t>
-  </si>
-  <si>
-    <t>0.0041,0.9426,0.4637,0.0005</t>
-  </si>
-  <si>
-    <t>0.0090,0.1181,0.9356,0.0334</t>
-  </si>
-  <si>
-    <t>0.2059,0.3476,0.0056,0.4675</t>
-  </si>
-  <si>
-    <t>0.0060,0.9734,0.0058,0.0140</t>
-  </si>
-  <si>
-    <t>0.0197,0.9187,0.2576,0.0035</t>
-  </si>
-  <si>
-    <t>0.0040,0.9769,0.0090,0.0114</t>
-  </si>
-  <si>
-    <t>0.0048,0.0098,0.9851,0.0058</t>
-  </si>
-  <si>
-    <t>0.0047,0.3182,0.9689,0.0019</t>
-  </si>
-  <si>
-    <t>0.0219,0.0149,0.9656,0.0059</t>
-  </si>
-  <si>
-    <t>0.0246,0.0039,0.9763,0.0052</t>
-  </si>
-  <si>
-    <t>0.0143,0.0327,0.9553,0.0172</t>
-  </si>
-  <si>
-    <t>0.0490,0.0206,0.9213,0.0122</t>
-  </si>
-  <si>
-    <t>0.9575,0.0496,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9639,0.0271,0.0071,0.0017</t>
-  </si>
-  <si>
-    <t>0.9693,0.0280,0.0032,0.0018</t>
-  </si>
-  <si>
-    <t>0.0077,0.0403,0.9722,0.0181</t>
-  </si>
-  <si>
-    <t>0.9766,0.0083,0.0069,0.0021</t>
-  </si>
-  <si>
-    <t>0.9922,0.0020,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9776,0.0253,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.8624,0.8762,0.0003</t>
-  </si>
-  <si>
-    <t>0.0189,0.3440,0.9239,0.0045</t>
-  </si>
-  <si>
-    <t>0.0043,0.0370,0.9826,0.0039</t>
-  </si>
-  <si>
-    <t>0.0012,0.8167,0.9580,0.0002</t>
-  </si>
-  <si>
-    <t>0.0052,0.0145,0.9865,0.0014</t>
-  </si>
-  <si>
-    <t>0.1827,0.8147,0.0398,0.0093</t>
-  </si>
-  <si>
-    <t>0.0302,0.9670,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9226,0.0140,0.0888,0.0037</t>
-  </si>
-  <si>
-    <t>0.8502,0.1401,0.0244,0.0049</t>
-  </si>
-  <si>
-    <t>0.0010,0.0129,0.9945,0.0018</t>
-  </si>
-  <si>
-    <t>0.0011,0.9236,0.7671,0.0001</t>
-  </si>
-  <si>
-    <t>0.0120,0.6194,0.7185,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.9863,0.5963,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.4341,0.9789,0.0012</t>
-  </si>
-  <si>
-    <t>0.1174,0.0033,0.0875,0.8492</t>
-  </si>
-  <si>
-    <t>0.0033,0.0007,0.0030,0.9967</t>
-  </si>
-  <si>
-    <t>0.0106,0.0046,0.0037,0.9923</t>
-  </si>
-  <si>
-    <t>0.0315,0.0010,0.0008,0.9912</t>
-  </si>
-  <si>
-    <t>0.1313,0.0252,0.0094,0.9157</t>
-  </si>
-  <si>
-    <t>0.0513,0.0056,0.0003,0.9825</t>
-  </si>
-  <si>
-    <t>0.0018,0.9364,0.6735,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9215,0.8473,0.0001</t>
-  </si>
-  <si>
-    <t>0.1285,0.6060,0.2868,0.0112</t>
-  </si>
-  <si>
-    <t>0.0074,0.1908,0.9621,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.9131,0.8536,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.8983,0.5792,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0025,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0064,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.9616,0.0626,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9830,0.0065,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9881,0.0096,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9934,0.0052,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9821,0.0153,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9835,0.0064,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9939,0.0028,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9963,0.0006,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9923,0.0037,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9849,0.0070,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.9905,0.0028,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9918,0.0023,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.0058,0.0034,0.9781,0.0223</t>
-  </si>
-  <si>
-    <t>0.1125,0.0203,0.8889,0.0044</t>
-  </si>
-  <si>
-    <t>0.8268,0.0128,0.1421,0.0269</t>
-  </si>
-  <si>
-    <t>0.1471,0.0051,0.9192,0.0032</t>
-  </si>
-  <si>
-    <t>0.1782,0.8691,0.0076,0.0009</t>
-  </si>
-  <si>
-    <t>0.1191,0.9000,0.0189,0.0005</t>
-  </si>
-  <si>
-    <t>0.2750,0.7647,0.0024,0.0041</t>
-  </si>
-  <si>
-    <t>0.4237,0.6775,0.0080,0.0025</t>
-  </si>
-  <si>
-    <t>0.2050,0.8527,0.0032,0.0018</t>
-  </si>
-  <si>
-    <t>0.1809,0.8526,0.0116,0.0008</t>
-  </si>
-  <si>
-    <t>0.7184,0.3483,0.0187,0.0009</t>
-  </si>
-  <si>
-    <t>0.6754,0.0778,0.2942,0.0405</t>
-  </si>
-  <si>
-    <t>0.4015,0.0126,0.6831,0.0256</t>
-  </si>
-  <si>
-    <t>0.1662,0.6952,0.1372,0.0526</t>
-  </si>
-  <si>
-    <t>0.6065,0.1505,0.3415,0.0444</t>
-  </si>
-  <si>
-    <t>0.1095,0.3244,0.0220,0.7995</t>
-  </si>
-  <si>
-    <t>0.0044,0.9739,0.0208,0.0180</t>
-  </si>
-  <si>
-    <t>0.0072,0.9664,0.0073,0.0281</t>
-  </si>
-  <si>
-    <t>0.2642,0.6401,0.1531,0.0558</t>
-  </si>
-  <si>
-    <t>0.0006,0.9318,0.8763,0.0011</t>
-  </si>
-  <si>
-    <t>0.0716,0.8961,0.0882,0.0003</t>
-  </si>
-  <si>
-    <t>0.8341,0.1477,0.0388,0.0019</t>
-  </si>
-  <si>
-    <t>0.4891,0.5630,0.0266,0.0005</t>
-  </si>
-  <si>
-    <t>0.9899,0.0066,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9799,0.0018,0.0007,0.0106</t>
-  </si>
-  <si>
-    <t>0.9871,0.0011,0.0009,0.0052</t>
-  </si>
-  <si>
-    <t>0.9703,0.0096,0.0089,0.0039</t>
-  </si>
-  <si>
-    <t>0.9844,0.0050,0.0012,0.0030</t>
-  </si>
-  <si>
-    <t>0.8910,0.0323,0.0948,0.0009</t>
-  </si>
-  <si>
-    <t>0.9894,0.0014,0.0004,0.0027</t>
-  </si>
-  <si>
-    <t>0.9846,0.0043,0.0020,0.0027</t>
-  </si>
-  <si>
-    <t>0.0082,0.7115,0.8896,0.0036</t>
-  </si>
-  <si>
-    <t>0.0045,0.2929,0.9690,0.0006</t>
-  </si>
-  <si>
-    <t>0.0063,0.2396,0.9666,0.0010</t>
-  </si>
-  <si>
-    <t>0.0780,0.1508,0.8217,0.0108</t>
-  </si>
-  <si>
-    <t>0.8789,0.0245,0.0412,0.0217</t>
-  </si>
-  <si>
-    <t>0.2095,0.0800,0.7843,0.0471</t>
-  </si>
-  <si>
-    <t>0.4129,0.0039,0.7414,0.0158</t>
-  </si>
-  <si>
-    <t>0.3633,0.1541,0.5475,0.0132</t>
-  </si>
-  <si>
-    <t>0.2362,0.0059,0.0034,0.8946</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.0021,0.0085,0.0050,0.9967</t>
-  </si>
-  <si>
-    <t>0.0331,0.0000,0.0045,0.9793</t>
-  </si>
-  <si>
-    <t>0.0019,0.8205,0.8942,0.0012</t>
-  </si>
-  <si>
-    <t>0.9649,0.0083,0.0015,0.0091</t>
-  </si>
-  <si>
-    <t>0.2025,0.7961,0.0069,0.0151</t>
-  </si>
-  <si>
-    <t>0.9894,0.0031,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.5892,0.5355,0.0056,0.0023</t>
-  </si>
-  <si>
-    <t>0.9530,0.0113,0.0121,0.0107</t>
-  </si>
-  <si>
-    <t>0.7527,0.0102,0.0801,0.1424</t>
-  </si>
-  <si>
-    <t>0.9824,0.0012,0.0012,0.0079</t>
-  </si>
-  <si>
-    <t>0.0035,0.4361,0.9442,0.0068</t>
-  </si>
-  <si>
-    <t>0.8107,0.0003,0.0089,0.1625</t>
-  </si>
-  <si>
-    <t>0.8735,0.0058,0.0114,0.0828</t>
-  </si>
-  <si>
-    <t>0.5430,0.5111,0.0330,0.0105</t>
-  </si>
-  <si>
-    <t>0.8706,0.0952,0.0252,0.0131</t>
-  </si>
-  <si>
-    <t>0.8937,0.0813,0.0258,0.0042</t>
-  </si>
-  <si>
-    <t>0.0970,0.8636,0.0084,0.0195</t>
-  </si>
-  <si>
-    <t>0.7318,0.3509,0.0081,0.0021</t>
-  </si>
-  <si>
-    <t>0.8810,0.0697,0.0512,0.0066</t>
-  </si>
-  <si>
-    <t>0.9921,0.0022,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9845,0.0133,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9896,0.0025,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9953,0.0013,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9861,0.0041,0.0034,0.0014</t>
-  </si>
-  <si>
-    <t>0.9810,0.0030,0.0016,0.0049</t>
-  </si>
-  <si>
-    <t>0.9907,0.0034,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9865,0.0028,0.0015,0.0025</t>
-  </si>
-  <si>
-    <t>0.4377,0.6156,0.0458,0.0073</t>
-  </si>
-  <si>
-    <t>0.7954,0.3560,0.0035,0.0004</t>
-  </si>
-  <si>
-    <t>0.4642,0.6704,0.0032,0.0019</t>
-  </si>
-  <si>
-    <t>0.0534,0.2373,0.8908,0.0012</t>
-  </si>
-  <si>
-    <t>0.9388,0.0564,0.0078,0.0026</t>
-  </si>
-  <si>
-    <t>0.9481,0.0355,0.0067,0.0038</t>
-  </si>
-  <si>
-    <t>0.9470,0.0152,0.0014,0.0129</t>
-  </si>
-  <si>
-    <t>0.9594,0.0113,0.0060,0.0116</t>
-  </si>
-  <si>
-    <t>0.0053,0.0162,0.9930,0.0005</t>
-  </si>
-  <si>
-    <t>0.9450,0.0308,0.0137,0.0032</t>
-  </si>
-  <si>
-    <t>0.0013,0.0035,0.9938,0.0039</t>
-  </si>
-  <si>
-    <t>0.0603,0.3433,0.7974,0.0358</t>
-  </si>
-  <si>
-    <t>0.0616,0.0134,0.9429,0.0067</t>
-  </si>
-  <si>
-    <t>0.0140,0.3301,0.9338,0.0076</t>
-  </si>
-  <si>
-    <t>0.0139,0.0742,0.9561,0.0014</t>
-  </si>
-  <si>
-    <t>0.0111,0.0053,0.9864,0.0006</t>
-  </si>
-  <si>
-    <t>0.0054,0.0126,0.9900,0.0003</t>
-  </si>
-  <si>
-    <t>0.2056,0.0193,0.8307,0.0146</t>
-  </si>
-  <si>
-    <t>0.0582,0.0135,0.9542,0.0022</t>
-  </si>
-  <si>
-    <t>0.5433,0.0189,0.5629,0.0163</t>
-  </si>
-  <si>
-    <t>0.0779,0.6826,0.3210,0.0020</t>
-  </si>
-  <si>
-    <t>0.3933,0.0265,0.7223,0.0073</t>
-  </si>
-  <si>
-    <t>0.4651,0.1554,0.4449,0.0166</t>
-  </si>
-  <si>
-    <t>0.6406,0.0256,0.4447,0.0136</t>
-  </si>
-  <si>
-    <t>0.2050,0.0511,0.8027,0.0158</t>
-  </si>
-  <si>
-    <t>0.5555,0.4608,0.0285,0.0005</t>
-  </si>
-  <si>
-    <t>0.6615,0.2905,0.0508,0.0015</t>
-  </si>
-  <si>
-    <t>0.9172,0.0981,0.0102,0.0015</t>
-  </si>
-  <si>
-    <t>0.9821,0.0253,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9649,0.0298,0.0059,0.0016</t>
-  </si>
-  <si>
-    <t>0.3059,0.5213,0.1483,0.0906</t>
-  </si>
-  <si>
-    <t>0.5836,0.2649,0.1798,0.0622</t>
-  </si>
-  <si>
-    <t>0.7894,0.0273,0.0536,0.0896</t>
-  </si>
-  <si>
-    <t>0.6221,0.0065,0.3947,0.0378</t>
-  </si>
-  <si>
-    <t>0.8282,0.0319,0.1012,0.0323</t>
-  </si>
-  <si>
-    <t>0.0284,0.0157,0.9500,0.0197</t>
-  </si>
-  <si>
-    <t>0.0280,0.0864,0.9032,0.0117</t>
-  </si>
-  <si>
-    <t>0.0270,0.4996,0.7408,0.0060</t>
-  </si>
-  <si>
-    <t>0.0318,0.0202,0.9438,0.0103</t>
-  </si>
-  <si>
-    <t>0.0505,0.2934,0.7080,0.0157</t>
-  </si>
-  <si>
-    <t>0.9866,0.0018,0.0002,0.0036</t>
-  </si>
-  <si>
-    <t>0.9580,0.0439,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.9871,0.0044,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9869,0.0177,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9739,0.0161,0.0063,0.0018</t>
-  </si>
-  <si>
-    <t>0.9820,0.0129,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9721,0.0140,0.0024,0.0029</t>
-  </si>
-  <si>
-    <t>0.9796,0.0099,0.0028,0.0020</t>
-  </si>
-  <si>
-    <t>0.1203,0.0655,0.8635,0.0034</t>
-  </si>
-  <si>
-    <t>0.2943,0.0423,0.7780,0.0069</t>
-  </si>
-  <si>
-    <t>0.8921,0.0761,0.0274,0.0064</t>
-  </si>
-  <si>
-    <t>0.0220,0.0146,0.9589,0.0087</t>
-  </si>
-  <si>
-    <t>0.0015,0.0226,0.9923,0.0014</t>
-  </si>
-  <si>
-    <t>0.0195,0.3809,0.8268,0.0044</t>
-  </si>
-  <si>
-    <t>0.0022,0.0080,0.9872,0.0037</t>
-  </si>
-  <si>
-    <t>0.1083,0.0746,0.7285,0.0054</t>
-  </si>
-  <si>
-    <t>0.0041,0.0051,0.9935,0.0007</t>
-  </si>
-  <si>
-    <t>0.0456,0.0723,0.8963,0.0082</t>
-  </si>
-  <si>
-    <t>0.0994,0.0238,0.8893,0.0035</t>
-  </si>
-  <si>
-    <t>0.7674,0.0047,0.2014,0.0304</t>
-  </si>
-  <si>
-    <t>0.4553,0.0165,0.6542,0.0236</t>
-  </si>
-  <si>
-    <t>0.9177,0.0022,0.0595,0.0099</t>
-  </si>
-  <si>
-    <t>0.9906,0.0053,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9906,0.0056,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.9895,0.0029,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9871,0.0020,0.0005,0.0034</t>
-  </si>
-  <si>
-    <t>0.9880,0.0011,0.0002,0.0044</t>
-  </si>
-  <si>
-    <t>0.9885,0.0124,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9926,0.0046,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9834,0.0049,0.0038,0.0023</t>
-  </si>
-  <si>
-    <t>0.0087,0.0337,0.9728,0.0011</t>
-  </si>
-  <si>
-    <t>0.0044,0.0052,0.9913,0.0019</t>
-  </si>
-  <si>
-    <t>0.0074,0.0393,0.9725,0.0062</t>
-  </si>
-  <si>
-    <t>0.0619,0.0739,0.8024,0.0217</t>
-  </si>
-  <si>
-    <t>0.0042,0.0076,0.9914,0.0010</t>
-  </si>
-  <si>
-    <t>0.1444,0.0193,0.8290,0.0598</t>
-  </si>
-  <si>
-    <t>0.0363,0.0175,0.6365,0.6465</t>
-  </si>
-  <si>
-    <t>0.0514,0.0625,0.8516,0.0889</t>
-  </si>
-  <si>
-    <t>0.5329,0.0016,0.0300,0.4724</t>
-  </si>
-  <si>
-    <t>0.0745,0.0040,0.0011,0.9795</t>
-  </si>
-  <si>
-    <t>0.0381,0.0327,0.0009,0.9750</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.0012,0.9980</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0037,0.9970</t>
-  </si>
-  <si>
-    <t>0.7420,0.0202,0.0112,0.2393</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.7301,0.0677,0.0379,0.1509</t>
+  </si>
+  <si>
+    <t>0.0013,0.0012,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.8462,0.0247,0.0353,0.0694</t>
+  </si>
+  <si>
+    <t>0.1498,0.0036,0.0178,0.9106</t>
+  </si>
+  <si>
+    <t>0.9969,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0027,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9726,0.0242,0.0040,0.0012</t>
+  </si>
+  <si>
+    <t>0.9909,0.0017,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.9911,0.0032,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9918,0.0033,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9946,0.0010,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.4171,0.1067,0.5295,0.0134</t>
+  </si>
+  <si>
+    <t>0.4873,0.0389,0.6112,0.0083</t>
+  </si>
+  <si>
+    <t>0.3615,0.0972,0.5926,0.0013</t>
+  </si>
+  <si>
+    <t>0.2514,0.0199,0.8034,0.0156</t>
+  </si>
+  <si>
+    <t>0.8738,0.0239,0.1145,0.0119</t>
+  </si>
+  <si>
+    <t>0.1253,0.9026,0.0093,0.0013</t>
+  </si>
+  <si>
+    <t>0.2602,0.8172,0.0182,0.0009</t>
+  </si>
+  <si>
+    <t>0.5530,0.5761,0.0122,0.0021</t>
+  </si>
+  <si>
+    <t>0.0726,0.9270,0.0072,0.0008</t>
+  </si>
+  <si>
+    <t>0.0401,0.9598,0.0128,0.0007</t>
+  </si>
+  <si>
+    <t>0.5079,0.0314,0.4145,0.0892</t>
+  </si>
+  <si>
+    <t>0.5937,0.0472,0.4016,0.0512</t>
+  </si>
+  <si>
+    <t>0.0136,0.0163,0.9621,0.0194</t>
+  </si>
+  <si>
+    <t>0.1090,0.0189,0.8844,0.0123</t>
+  </si>
+  <si>
+    <t>0.0670,0.0104,0.9474,0.0026</t>
+  </si>
+  <si>
+    <t>0.0760,0.0038,0.9425,0.0040</t>
+  </si>
+  <si>
+    <t>0.0034,0.0012,0.9892,0.0149</t>
+  </si>
+  <si>
+    <t>0.7676,0.2584,0.0261,0.0029</t>
+  </si>
+  <si>
+    <t>0.4176,0.5153,0.1631,0.0072</t>
+  </si>
+  <si>
+    <t>0.0026,0.0107,0.9864,0.0106</t>
+  </si>
+  <si>
+    <t>0.0310,0.8262,0.3204,0.0008</t>
+  </si>
+  <si>
+    <t>0.7098,0.2691,0.0648,0.0164</t>
+  </si>
+  <si>
+    <t>0.8627,0.0675,0.0829,0.0069</t>
+  </si>
+  <si>
+    <t>0.5280,0.5658,0.0132,0.0023</t>
+  </si>
+  <si>
+    <t>0.0637,0.8781,0.1894,0.0112</t>
+  </si>
+  <si>
+    <t>0.0207,0.1633,0.6837,0.1698</t>
+  </si>
+  <si>
+    <t>0.1232,0.0113,0.7822,0.0492</t>
+  </si>
+  <si>
+    <t>0.0445,0.2827,0.8254,0.0131</t>
+  </si>
+  <si>
+    <t>0.0868,0.0287,0.8891,0.0043</t>
+  </si>
+  <si>
+    <t>0.0244,0.1025,0.9305,0.0121</t>
+  </si>
+  <si>
+    <t>0.0041,0.9659,0.0334,0.0028</t>
+  </si>
+  <si>
+    <t>0.0258,0.0924,0.9227,0.0111</t>
+  </si>
+  <si>
+    <t>0.3198,0.4563,0.1620,0.4597</t>
+  </si>
+  <si>
+    <t>0.0138,0.9589,0.0193,0.0102</t>
+  </si>
+  <si>
+    <t>0.0095,0.9518,0.1960,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.9670,0.0273,0.0669</t>
+  </si>
+  <si>
+    <t>0.0103,0.1169,0.7821,0.0936</t>
+  </si>
+  <si>
+    <t>0.0046,0.0454,0.9860,0.0017</t>
+  </si>
+  <si>
+    <t>0.0078,0.0010,0.9871,0.0074</t>
+  </si>
+  <si>
+    <t>0.0712,0.0169,0.9157,0.0117</t>
+  </si>
+  <si>
+    <t>0.0003,0.0067,0.9968,0.0011</t>
+  </si>
+  <si>
+    <t>0.0081,0.0017,0.9912,0.0007</t>
+  </si>
+  <si>
+    <t>0.9573,0.0436,0.0046,0.0014</t>
+  </si>
+  <si>
+    <t>0.9685,0.0093,0.0100,0.0045</t>
+  </si>
+  <si>
+    <t>0.9616,0.0276,0.0074,0.0024</t>
+  </si>
+  <si>
+    <t>0.0147,0.0847,0.9734,0.0034</t>
+  </si>
+  <si>
+    <t>0.9911,0.0032,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9759,0.0114,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.7185,0.3905,0.0116,0.0015</t>
+  </si>
+  <si>
+    <t>0.0006,0.9316,0.9399,0.0001</t>
+  </si>
+  <si>
+    <t>0.0119,0.0997,0.9813,0.0007</t>
+  </si>
+  <si>
+    <t>0.0048,0.0085,0.9761,0.0207</t>
+  </si>
+  <si>
+    <t>0.0012,0.8460,0.9485,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0014,0.9938,0.0068</t>
+  </si>
+  <si>
+    <t>0.0475,0.8827,0.1114,0.0057</t>
+  </si>
+  <si>
+    <t>0.0148,0.9814,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.9121,0.0211,0.0927,0.0045</t>
+  </si>
+  <si>
+    <t>0.8449,0.0703,0.0662,0.0165</t>
+  </si>
+  <si>
+    <t>0.0014,0.0873,0.9907,0.0010</t>
+  </si>
+  <si>
+    <t>0.0036,0.8407,0.6464,0.0008</t>
+  </si>
+  <si>
+    <t>0.0260,0.4873,0.8134,0.0051</t>
+  </si>
+  <si>
+    <t>0.0009,0.9592,0.8236,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.8614,0.8566,0.0035</t>
+  </si>
+  <si>
+    <t>0.0731,0.0007,0.0152,0.9443</t>
+  </si>
+  <si>
+    <t>0.0054,0.0063,0.0010,0.9967</t>
+  </si>
+  <si>
+    <t>0.0220,0.0027,0.0034,0.9885</t>
+  </si>
+  <si>
+    <t>0.0215,0.0117,0.0356,0.9706</t>
+  </si>
+  <si>
+    <t>0.0301,0.0007,0.0341,0.9576</t>
+  </si>
+  <si>
+    <t>0.0064,0.0056,0.0040,0.9944</t>
+  </si>
+  <si>
+    <t>0.0023,0.9466,0.8062,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.6253,0.8649,0.0009</t>
+  </si>
+  <si>
+    <t>0.0206,0.4793,0.7897,0.0039</t>
+  </si>
+  <si>
+    <t>0.0135,0.3131,0.9179,0.0071</t>
+  </si>
+  <si>
+    <t>0.0007,0.9714,0.6207,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.6105,0.8561,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9830,0.0176,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9314,0.0980,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.9909,0.0030,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9788,0.0164,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.9970,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9738,0.0167,0.0013,0.0025</t>
+  </si>
+  <si>
+    <t>0.9874,0.0094,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9923,0.0011,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9951,0.0039,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9911,0.0016,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.9962,0.0013,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9912,0.0045,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9925,0.0013,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9930,0.0032,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0353,0.0481,0.9369,0.0032</t>
+  </si>
+  <si>
+    <t>0.0313,0.0171,0.9253,0.0684</t>
+  </si>
+  <si>
+    <t>0.6357,0.0194,0.0138,0.3608</t>
+  </si>
+  <si>
+    <t>0.0657,0.0087,0.9390,0.0016</t>
+  </si>
+  <si>
+    <t>0.0328,0.9612,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.0415,0.9265,0.0613,0.0008</t>
+  </si>
+  <si>
+    <t>0.0779,0.9078,0.0020,0.0051</t>
+  </si>
+  <si>
+    <t>0.6345,0.4601,0.0154,0.0012</t>
+  </si>
+  <si>
+    <t>0.4206,0.6774,0.0086,0.0019</t>
+  </si>
+  <si>
+    <t>0.0343,0.9631,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.3891,0.7417,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.3483,0.5556,0.1384,0.0925</t>
+  </si>
+  <si>
+    <t>0.1130,0.0058,0.9424,0.0026</t>
+  </si>
+  <si>
+    <t>0.5310,0.2735,0.2169,0.0165</t>
+  </si>
+  <si>
+    <t>0.3167,0.5328,0.2594,0.0269</t>
+  </si>
+  <si>
+    <t>0.3335,0.0904,0.2725,0.4115</t>
+  </si>
+  <si>
+    <t>0.0118,0.9627,0.0347,0.0117</t>
+  </si>
+  <si>
+    <t>0.0126,0.9626,0.0233,0.0121</t>
+  </si>
+  <si>
+    <t>0.0265,0.9267,0.0094,0.0566</t>
+  </si>
+  <si>
+    <t>0.0004,0.8366,0.9774,0.0001</t>
+  </si>
+  <si>
+    <t>0.1065,0.8878,0.0612,0.0005</t>
+  </si>
+  <si>
+    <t>0.6094,0.3891,0.0441,0.0010</t>
+  </si>
+  <si>
+    <t>0.4832,0.5160,0.0592,0.0060</t>
+  </si>
+  <si>
+    <t>0.9748,0.0092,0.0045,0.0040</t>
+  </si>
+  <si>
+    <t>0.9766,0.0064,0.0036,0.0046</t>
+  </si>
+  <si>
+    <t>0.9929,0.0009,0.0002,0.0019</t>
+  </si>
+  <si>
+    <t>0.9750,0.0065,0.0007,0.0051</t>
+  </si>
+  <si>
+    <t>0.9872,0.0021,0.0008,0.0043</t>
+  </si>
+  <si>
+    <t>0.9649,0.0384,0.0083,0.0012</t>
+  </si>
+  <si>
+    <t>0.9928,0.0014,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9912,0.0013,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.0047,0.8202,0.8488,0.0032</t>
+  </si>
+  <si>
+    <t>0.0006,0.7888,0.9514,0.0001</t>
+  </si>
+  <si>
+    <t>0.0304,0.1061,0.9285,0.0009</t>
+  </si>
+  <si>
+    <t>0.0496,0.3729,0.5886,0.0020</t>
+  </si>
+  <si>
+    <t>0.8432,0.0391,0.0706,0.0239</t>
+  </si>
+  <si>
+    <t>0.4690,0.0396,0.6443,0.0055</t>
+  </si>
+  <si>
+    <t>0.1471,0.0131,0.9139,0.0085</t>
+  </si>
+  <si>
+    <t>0.8268,0.0286,0.1982,0.0052</t>
+  </si>
+  <si>
+    <t>0.2139,0.0013,0.0003,0.9425</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0010,0.9996</t>
+  </si>
+  <si>
+    <t>0.0096,0.1331,0.0048,0.9862</t>
+  </si>
+  <si>
+    <t>0.1382,0.0011,0.0082,0.9326</t>
+  </si>
+  <si>
+    <t>0.0025,0.8846,0.8750,0.0014</t>
+  </si>
+  <si>
+    <t>0.9820,0.0060,0.0008,0.0031</t>
+  </si>
+  <si>
+    <t>0.8013,0.1603,0.0560,0.0275</t>
+  </si>
+  <si>
+    <t>0.9033,0.0297,0.0010,0.0233</t>
+  </si>
+  <si>
+    <t>0.6501,0.4610,0.0148,0.0023</t>
+  </si>
+  <si>
+    <t>0.9756,0.0083,0.0085,0.0023</t>
+  </si>
+  <si>
+    <t>0.5432,0.0075,0.0817,0.3840</t>
+  </si>
+  <si>
+    <t>0.9769,0.0131,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.0010,0.0340,0.9712,0.0304</t>
+  </si>
+  <si>
+    <t>0.8807,0.0005,0.0054,0.1155</t>
+  </si>
+  <si>
+    <t>0.8999,0.0008,0.0039,0.0908</t>
+  </si>
+  <si>
+    <t>0.8298,0.1068,0.0606,0.0162</t>
+  </si>
+  <si>
+    <t>0.9277,0.0412,0.0181,0.0047</t>
+  </si>
+  <si>
+    <t>0.8278,0.1638,0.0330,0.0046</t>
+  </si>
+  <si>
+    <t>0.7294,0.1273,0.1799,0.0057</t>
+  </si>
+  <si>
+    <t>0.8083,0.0651,0.1899,0.0036</t>
+  </si>
+  <si>
+    <t>0.8190,0.1724,0.0371,0.0093</t>
+  </si>
+  <si>
+    <t>0.9900,0.0026,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9585,0.0236,0.0064,0.0043</t>
+  </si>
+  <si>
+    <t>0.9899,0.0031,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9924,0.0007,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9832,0.0102,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9841,0.0071,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9817,0.0090,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.9829,0.0053,0.0018,0.0021</t>
+  </si>
+  <si>
+    <t>0.2610,0.7883,0.0081,0.0054</t>
+  </si>
+  <si>
+    <t>0.7833,0.2659,0.0206,0.0038</t>
+  </si>
+  <si>
+    <t>0.7720,0.3127,0.0138,0.0010</t>
+  </si>
+  <si>
+    <t>0.3340,0.4606,0.2619,0.0066</t>
+  </si>
+  <si>
+    <t>0.9502,0.0522,0.0094,0.0011</t>
+  </si>
+  <si>
+    <t>0.9688,0.0075,0.0050,0.0081</t>
+  </si>
+  <si>
+    <t>0.9549,0.0266,0.0115,0.0043</t>
+  </si>
+  <si>
+    <t>0.9576,0.0215,0.0018,0.0051</t>
+  </si>
+  <si>
+    <t>0.0063,0.0388,0.9902,0.0009</t>
+  </si>
+  <si>
+    <t>0.9536,0.0332,0.0106,0.0035</t>
+  </si>
+  <si>
+    <t>0.0113,0.0243,0.9737,0.0030</t>
+  </si>
+  <si>
+    <t>0.1237,0.2160,0.7267,0.0085</t>
+  </si>
+  <si>
+    <t>0.2250,0.0113,0.8710,0.0063</t>
+  </si>
+  <si>
+    <t>0.0020,0.0289,0.9733,0.0117</t>
+  </si>
+  <si>
+    <t>0.0169,0.0561,0.9565,0.0010</t>
+  </si>
+  <si>
+    <t>0.0117,0.0013,0.9906,0.0007</t>
+  </si>
+  <si>
+    <t>0.0060,0.0029,0.9921,0.0010</t>
+  </si>
+  <si>
+    <t>0.1506,0.0218,0.8673,0.0095</t>
+  </si>
+  <si>
+    <t>0.3043,0.0237,0.7873,0.0050</t>
+  </si>
+  <si>
+    <t>0.6864,0.0233,0.4498,0.0042</t>
+  </si>
+  <si>
+    <t>0.5550,0.2124,0.1797,0.0032</t>
+  </si>
+  <si>
+    <t>0.4493,0.0291,0.6713,0.0038</t>
+  </si>
+  <si>
+    <t>0.7527,0.0520,0.2597,0.0023</t>
+  </si>
+  <si>
+    <t>0.6785,0.0486,0.3614,0.0218</t>
+  </si>
+  <si>
+    <t>0.1539,0.0699,0.8006,0.0047</t>
+  </si>
+  <si>
+    <t>0.9007,0.1276,0.0120,0.0008</t>
+  </si>
+  <si>
+    <t>0.9095,0.1134,0.0092,0.0015</t>
+  </si>
+  <si>
+    <t>0.8011,0.2079,0.0218,0.0005</t>
+  </si>
+  <si>
+    <t>0.9759,0.0288,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9728,0.0353,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.6219,0.1570,0.2663,0.0265</t>
+  </si>
+  <si>
+    <t>0.6828,0.0219,0.4491,0.0072</t>
+  </si>
+  <si>
+    <t>0.5086,0.1821,0.1377,0.1832</t>
+  </si>
+  <si>
+    <t>0.6676,0.0052,0.3700,0.0260</t>
+  </si>
+  <si>
+    <t>0.8816,0.0050,0.0999,0.0184</t>
+  </si>
+  <si>
+    <t>0.0041,0.0043,0.9855,0.0212</t>
+  </si>
+  <si>
+    <t>0.0347,0.0985,0.8518,0.0706</t>
+  </si>
+  <si>
+    <t>0.0398,0.2891,0.7339,0.1243</t>
+  </si>
+  <si>
+    <t>0.1761,0.0812,0.7663,0.0074</t>
+  </si>
+  <si>
+    <t>0.0222,0.1150,0.8980,0.0033</t>
+  </si>
+  <si>
+    <t>0.9889,0.0083,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9826,0.0271,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9852,0.0102,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9807,0.0119,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9772,0.0149,0.0047,0.0014</t>
+  </si>
+  <si>
+    <t>0.9871,0.0023,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9899,0.0022,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.2358,0.0401,0.8080,0.0051</t>
+  </si>
+  <si>
+    <t>0.4993,0.1491,0.4822,0.0186</t>
+  </si>
+  <si>
+    <t>0.8084,0.0663,0.1565,0.0154</t>
+  </si>
+  <si>
+    <t>0.0066,0.0465,0.9779,0.0026</t>
+  </si>
+  <si>
+    <t>0.0014,0.0129,0.9930,0.0015</t>
+  </si>
+  <si>
+    <t>0.0099,0.2931,0.8896,0.0035</t>
+  </si>
+  <si>
+    <t>0.0073,0.0113,0.9800,0.0064</t>
+  </si>
+  <si>
+    <t>0.0660,0.0396,0.9050,0.0039</t>
+  </si>
+  <si>
+    <t>0.0014,0.0189,0.9937,0.0006</t>
+  </si>
+  <si>
+    <t>0.0226,0.1234,0.8686,0.0091</t>
+  </si>
+  <si>
+    <t>0.0938,0.0734,0.8191,0.0117</t>
+  </si>
+  <si>
+    <t>0.4293,0.0105,0.7141,0.0116</t>
+  </si>
+  <si>
+    <t>0.2115,0.0019,0.9050,0.0056</t>
+  </si>
+  <si>
+    <t>0.7835,0.0035,0.2699,0.0131</t>
+  </si>
+  <si>
+    <t>0.9815,0.0097,0.0013,0.0021</t>
+  </si>
+  <si>
+    <t>0.9942,0.0028,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9860,0.0089,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9871,0.0084,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9717,0.0164,0.0036,0.0023</t>
+  </si>
+  <si>
+    <t>0.9871,0.0081,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.9890,0.0146,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9877,0.0023,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.0614,0.1575,0.7646,0.0253</t>
+  </si>
+  <si>
+    <t>0.0065,0.0772,0.9713,0.0011</t>
+  </si>
+  <si>
+    <t>0.0117,0.0967,0.9016,0.0142</t>
+  </si>
+  <si>
+    <t>0.0696,0.0124,0.9292,0.0069</t>
+  </si>
+  <si>
+    <t>0.0287,0.0136,0.9527,0.0113</t>
+  </si>
+  <si>
+    <t>0.2589,0.0056,0.4868,0.2024</t>
+  </si>
+  <si>
+    <t>0.2317,0.0061,0.8760,0.0040</t>
+  </si>
+  <si>
+    <t>0.0090,0.0148,0.9320,0.1075</t>
+  </si>
+  <si>
+    <t>0.6411,0.0019,0.0046,0.5413</t>
+  </si>
+  <si>
+    <t>0.0285,0.0009,0.0022,0.9879</t>
+  </si>
+  <si>
+    <t>0.0735,0.0006,0.0068,0.9608</t>
+  </si>
+  <si>
+    <t>0.0080,0.0001,0.0004,0.9972</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.0009,0.9991</t>
+  </si>
+  <si>
+    <t>0.7804,0.0777,0.0931,0.0701</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +2998,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,10 +5420,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
